--- a/MetadataSync/orch_metadata.xlsx
+++ b/MetadataSync/orch_metadata.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25180" windowHeight="16140" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ObjectIDs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TaskType" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JobDependencies" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TaskDependencies" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DependencyCondition" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JobDependencies" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TaskDependencies" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TaskType" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ObjectIDs" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="JobNameList">Jobs!$A$2:$A$1000</definedName>
-    <definedName name="ObjectNameList">ObjectIDs!$B$2:$B$1000</definedName>
+    <definedName name="TaskNameList">Tasks!$A$2:$A$1000</definedName>
     <definedName name="TaskTypeList">TaskType!$A$2:$A$1000</definedName>
     <definedName name="WorkspaceNameList">ObjectIDs!$A$2:$A$1000</definedName>
+    <definedName name="ObjectNameList">ObjectIDs!$B$2:$B$1000</definedName>
     <definedName name="DependencyConditionList">DependencyCondition!$A$2:$A$1000</definedName>
-    <definedName name="TaskNameList">Tasks!$A$2:$A$1000</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -38,10 +39,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="9">
@@ -53,41 +52,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBF8F00"/>
-        <bgColor rgb="FFBF8F00"/>
+        <fgColor rgb="002F5597"/>
+        <bgColor rgb="002F5597"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
-        <bgColor rgb="FF7030A0"/>
+        <fgColor rgb="00548235"/>
+        <bgColor rgb="00548235"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5597"/>
-        <bgColor rgb="FF2F5597"/>
+        <fgColor rgb="0031859B"/>
+        <bgColor rgb="0031859B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF548235"/>
-        <bgColor rgb="FF548235"/>
+        <fgColor rgb="00C55A11"/>
+        <bgColor rgb="00C55A11"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
+        <fgColor rgb="00808080"/>
+        <bgColor rgb="00808080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
+        <fgColor rgb="007030A0"/>
+        <bgColor rgb="007030A0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF375623"/>
+        <fgColor rgb="00BF8F00"/>
+        <bgColor rgb="00BF8F00"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,12 +119,18 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -206,26 +214,78 @@
       <text>
         <t>Type: VARCHAR(200)
 Nullable: No
-PK (1/2)</t>
+PK</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
+        <t>Type: BIT
+Nullable: No
+Default: 1</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: INT
+Nullable: No</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: INT
+Nullable: No</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: INT
+Nullable: No</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: INT
+Nullable: No
+Default: 4</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: TIME(0)
+Nullable: Yes</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: NVARCHAR(MAX)
+Nullable: Yes</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: NVARCHAR(MAX)
+Nullable: Yes</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
         <t>Type: VARCHAR(200)
+Nullable: Yes
+FK -&gt; orch.ObjectIDs (WorkspaceName,JobName)=(WorkspaceName,ObjectName)</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: NVARCHAR(100)
+Nullable: Yes</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: TINYINT
 Nullable: No
-PK (2/2)</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: VARCHAR(200)
-Nullable: No</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: VARCHAR(200)
-Nullable: Yes</t>
+Default: 1
+FK -&gt; log.LoggingLevel</t>
       </text>
     </comment>
   </commentList>
@@ -240,7 +300,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Type: NVARCHAR(50)
+        <t>Type: NVARCHAR(200)
 Nullable: No
 PK</t>
       </text>
@@ -250,6 +310,84 @@
         <t>Type: BIT
 Nullable: No
 Default: 1</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: VARCHAR(200)
+Nullable: No
+FK -&gt; orch.Jobs</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: VARCHAR(200)
+Nullable: No
+FK -&gt; orch.ObjectIDs (composite w/ WorkspaceName)</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: VARCHAR(200)
+Nullable: Yes
+FK -&gt; orch.ObjectIDs (composite)</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: INT
+Nullable: No</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: INT
+Nullable: No</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: INT
+Nullable: No</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: NVARCHAR(MAX)
+Nullable: Yes</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: NVARCHAR(MAX)
+Nullable: Yes</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: NVARCHAR(50)
+Nullable: No
+FK -&gt; orch.TaskType</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: NVARCHAR(100)
+Nullable: Yes</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: NVARCHAR(100)
+Nullable: Yes</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: TINYINT
+Nullable: No
+Default: 1
+FK -&gt; log.LoggingLevel</t>
       </text>
     </comment>
   </commentList>
@@ -266,71 +404,21 @@
       <text>
         <t>Type: VARCHAR(200)
 Nullable: No
-PK</t>
+PK (1/2), FK -&gt; orch.Jobs</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Type: BIT
+        <t>Type: VARCHAR(200)
 Nullable: No
-Default: 1</t>
+PK (2/2), FK -&gt; orch.Jobs</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Type: INT
-Nullable: No</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: INT
-Nullable: No</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: INT
-Nullable: No</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: TIME(0)
-Nullable: Yes</t>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: NVARCHAR(MAX)
-Nullable: Yes</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: NVARCHAR(MAX)
-Nullable: Yes</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: VARCHAR(200)
-Nullable: Yes
-FK -&gt; orch.ObjectIDs (WorkspaceName,JobName)=(WorkspaceName,ObjectName)</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: NVARCHAR(100)
-Nullable: Yes</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: TINYINT
+        <t>Type: VARCHAR(20)
 Nullable: No
-Default: 1
-FK -&gt; log.LoggingLevel</t>
+FK -&gt; orch.DependencyCondition</t>
       </text>
     </comment>
   </commentList>
@@ -345,7 +433,55 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Type: NVARCHAR(200)
+        <t>Type: VARCHAR(200)
+Nullable: No
+PK (1/2), FK -&gt; orch.Tasks</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: VARCHAR(200)
+Nullable: No
+PK (2/2), FK -&gt; orch.Tasks</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: VARCHAR(20)
+Nullable: No
+FK -&gt; orch.DependencyCondition</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Schema</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: VARCHAR(20)
+Nullable: No
+PK</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Schema</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: NVARCHAR(50)
 Nullable: No
 PK</t>
       </text>
@@ -357,82 +493,40 @@
 Default: 1</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Schema</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>Type: VARCHAR(200)
 Nullable: No
-FK -&gt; orch.Jobs</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+PK (1/2)</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>Type: VARCHAR(200)
 Nullable: No
-FK -&gt; orch.ObjectIDs (composite w/ WorkspaceName)</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+PK (2/2)</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>Type: VARCHAR(200)
-Nullable: Yes
-FK -&gt; orch.ObjectIDs (composite)</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: INT
 Nullable: No</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: INT
-Nullable: No</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: INT
-Nullable: No</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: NVARCHAR(MAX)
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: VARCHAR(200)
 Nullable: Yes</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: NVARCHAR(MAX)
-Nullable: Yes</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: NVARCHAR(50)
-Nullable: No
-FK -&gt; orch.TaskType</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: NVARCHAR(100)
-Nullable: Yes</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: NVARCHAR(100)
-Nullable: Yes</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>Type: TINYINT
-Nullable: No
-Default: 1
-FK -&gt; log.LoggingLevel</t>
       </text>
     </comment>
   </commentList>
@@ -440,52 +534,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblObjectIDs" displayName="tblObjectIDs" ref="A1:D4" headerRowCount="1">
-  <autoFilter ref="A1:D4"/>
-  <tableColumns count="4">
-    <tableColumn id="1" name="WorkspaceName"/>
-    <tableColumn id="2" name="ObjectName"/>
-    <tableColumn id="3" name="ObjectID"/>
-    <tableColumn id="4" name="WorkspaceID"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblJobs" displayName="tblJobs" ref="A1:L2" headerRowCount="1">
+  <autoFilter ref="A1:L2"/>
+  <tableColumns count="12">
+    <tableColumn id="1" name="JobName"/>
+    <tableColumn id="2" name="Include"/>
+    <tableColumn id="3" name="TimeoutInSeconds"/>
+    <tableColumn id="4" name="Retries"/>
+    <tableColumn id="5" name="RetryIntervalInSeconds"/>
+    <tableColumn id="6" name="ParallelBatchLimit"/>
+    <tableColumn id="7" name="ScheduledStartUTC"/>
+    <tableColumn id="8" name="ParametersJson"/>
+    <tableColumn id="9" name="Dependencies"/>
+    <tableColumn id="10" name="WorkspaceName"/>
+    <tableColumn id="11" name="Environment"/>
+    <tableColumn id="12" name="LoggingLevel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblTaskType" displayName="tblTaskType" ref="A1:B2" headerRowCount="1">
-  <autoFilter ref="A1:B2"/>
-  <tableColumns count="2">
-    <tableColumn id="1" name="TaskType"/>
-    <tableColumn id="2" name="AllowParallel"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblJobs" displayName="tblJobs" ref="A1:K2" headerRowCount="1">
-  <autoFilter ref="A1:K2"/>
-  <tableColumns count="11">
-    <tableColumn id="1" name="JobName"/>
-    <tableColumn id="2" name="Include"/>
-    <tableColumn id="3" name="TimeoutInSeconds"/>
-    <tableColumn id="4" name="Retries"/>
-    <tableColumn id="5" name="RetryIntervalInSeconds"/>
-    <tableColumn id="6" name="ScheduledStartUTC"/>
-    <tableColumn id="7" name="ParametersJson"/>
-    <tableColumn id="8" name="Dependencies"/>
-    <tableColumn id="9" name="WorkspaceName"/>
-    <tableColumn id="10" name="Environment"/>
-    <tableColumn id="11" name="LoggingLevel"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblTasks" displayName="tblTasks" ref="A1:N28" headerRowCount="1">
-  <autoFilter ref="A1:N28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblTasks" displayName="tblTasks" ref="A1:N28" headerRowCount="1">
+  <autoFilter ref="A1:N2"/>
   <tableColumns count="14">
     <tableColumn id="1" name="TaskName"/>
     <tableColumn id="2" name="Include"/>
@@ -506,18 +577,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tblDependencyCondition" displayName="tblDependencyCondition" ref="A1:A4" headerRowCount="1">
-  <autoFilter ref="A1:A4"/>
-  <tableColumns count="1">
-    <tableColumn id="1" name="DependencyCondition"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tblJobDependencies" displayName="tblJobDependencies" ref="A1:C2" headerRowCount="1">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblJobDependencies" displayName="tblJobDependencies" ref="A1:C2" headerRowCount="1">
   <autoFilter ref="A1:C2"/>
   <tableColumns count="3">
     <tableColumn id="1" name="JobName"/>
@@ -528,13 +589,47 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblTaskDependencies" displayName="tblTaskDependencies" ref="A1:C2" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblTaskDependencies" displayName="tblTaskDependencies" ref="A1:C2" headerRowCount="1">
   <autoFilter ref="A1:C2"/>
   <tableColumns count="3">
     <tableColumn id="1" name="TaskName"/>
     <tableColumn id="2" name="DependentTaskName"/>
     <tableColumn id="3" name="DependsOn"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tblDependencyCondition" displayName="tblDependencyCondition" ref="A1:A4" headerRowCount="1">
+  <autoFilter ref="A1:A2"/>
+  <tableColumns count="1">
+    <tableColumn id="1" name="DependencyCondition"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="tblTaskType" displayName="tblTaskType" ref="A1:B2" headerRowCount="1">
+  <autoFilter ref="A1:B2"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="TaskType"/>
+    <tableColumn id="2" name="AllowParallel"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblObjectIDs" displayName="tblObjectIDs" ref="A1:D4" headerRowCount="1">
+  <autoFilter ref="A1:D2"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="WorkspaceName"/>
+    <tableColumn id="2" name="ObjectName"/>
+    <tableColumn id="3" name="ObjectID"/>
+    <tableColumn id="4" name="WorkspaceID"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -826,108 +921,133 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FFBF8F00"/>
+    <tabColor rgb="002F5597"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.7265625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="20.81640625" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="33.36328125" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="34.453125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>JobName</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>TimeoutInSeconds</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Retries</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>RetryIntervalInSeconds</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ParallelBatchLimit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ScheduledStartUTC</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ParametersJson</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>WorkspaceName</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ObjectName</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ObjectID</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>WorkspaceID</t>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LoggingLevel</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Ingest_ContosoDW_Bronze</t>
+        </is>
+      </c>
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3600</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>60</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>Wave MDF CentralHub</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>nb_CopyTableToBronze</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PENDING_DEPLOYMENT_REPLACE_ME_nb_CopyTableToBronze</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>a937b42f-1407-41c9-b5bf-33288dc7f60f</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Wave MDF CentralHub</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>nb_RefreshObjectIDs</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PENDING_DEPLOYMENT_REPLACE_ME_nb_RefreshObjectIDs</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>a937b42f-1407-41c9-b5bf-33288dc7f60f</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wave MDF CentralHub</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ingest_ContosoDW_Bronze</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PENDING_DEPLOYMENT_REPLACE_ME_Ingest_ContosoDW_Bronze</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>a937b42f-1407-41c9-b5bf-33288dc7f60f</t>
-        </is>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>WorkspaceNameList</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
@@ -939,275 +1059,96 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF7030A0"/>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:N28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
+          <t>TaskName</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Include</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>JobName</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>ObjectName</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>WorkspaceName</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>TimeoutInSeconds</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Retries</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>RetryIntervalInSeconds</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>ParametersJson</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Dependencies</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
           <t>TaskType</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>AllowParallel</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Notebook</t>
-        </is>
-      </c>
-      <c r="B2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF2F5597"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="23.90625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.453125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="20.90625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="11.1796875" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="24.90625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="21.54296875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="18.81640625" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="17.08984375" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="19.7265625" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="16.1796875" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="15.7265625" bestFit="1" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>JobName</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>TimeoutInSeconds</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Retries</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>RetryIntervalInSeconds</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>ScheduledStartUTC</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>ParametersJson</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>WorkspaceName</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Environment</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>LoggingLevel</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ingest_ContosoDW_Bronze</t>
-        </is>
-      </c>
-      <c r="B2" t="b">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3600</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>60</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Wave MDF CentralHub</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>DEV</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>WorkspaceNameList</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF548235"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
-  <cols>
-    <col width="32.26953125" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="11.453125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="23.90625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="20.81640625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="19.7265625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="20.90625" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="11.1796875" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="24.90625" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="58" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="17.08984375" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="13.1796875" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="11.36328125" bestFit="1" customWidth="1" min="12" max="12"/>
-    <col width="9.81640625" bestFit="1" customWidth="1" min="13" max="13"/>
-    <col width="15.7265625" bestFit="1" customWidth="1" min="14" max="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>TaskName</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Include</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>JobName</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>ObjectName</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>WorkspaceName</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>TimeoutInSeconds</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Retries</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>RetryIntervalInSeconds</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>ParametersJson</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>TaskType</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>System</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>LoggingLevel</t>
         </is>
@@ -2778,80 +2719,33 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>DependencyCondition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Succeeded</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+    <tabColor rgb="0031859B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23.90625" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>JobName</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>DependentJobName</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>DependsOn</t>
         </is>
@@ -2870,38 +2764,40 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C55A11"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32.26953125" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>TaskName</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>DependentTaskName</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>DependsOn</t>
         </is>
@@ -2920,6 +2816,220 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>DependencyCondition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Succeeded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>TaskType</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>AllowParallel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Notebook</t>
+        </is>
+      </c>
+      <c r="B2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00BF8F00"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>WorkspaceName</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>ObjectName</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>ObjectID</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>WorkspaceID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Wave MDF CentralHub</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>nb_CopyTableToBronze</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PENDING_DEPLOYMENT_REPLACE_ME_nb_CopyTableToBronze</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>a937b42f-1407-41c9-b5bf-33288dc7f60f</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Wave MDF CentralHub</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>nb_RefreshObjectIDs</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PENDING_DEPLOYMENT_REPLACE_ME_nb_RefreshObjectIDs</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>a937b42f-1407-41c9-b5bf-33288dc7f60f</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wave MDF CentralHub</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ingest_ContosoDW_Bronze</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PENDING_DEPLOYMENT_REPLACE_ME_Ingest_ContosoDW_Bronze</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>a937b42f-1407-41c9-b5bf-33288dc7f60f</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>

--- a/MetadataSync/orch_metadata.xlsx
+++ b/MetadataSync/orch_metadata.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="19410" yWindow="-21720" windowWidth="51840" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,21 +16,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ObjectIDs" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="DependencyConditionList">DependencyCondition!$A$2:$A$1000</definedName>
     <definedName name="JobNameList">Jobs!$A$2:$A$1000</definedName>
-    <definedName name="ObjectNameList">ObjectIDs!$B$2:$B$1000</definedName>
     <definedName name="TaskNameList">Tasks!$A$2:$A$1000</definedName>
     <definedName name="TaskTypeList">TaskType!$A$2:$A$1000</definedName>
     <definedName name="WorkspaceNameList">ObjectIDs!$A$2:$A$1000</definedName>
+    <definedName name="ObjectNameList">ObjectIDs!$B$2:$B$1000</definedName>
+    <definedName name="DependencyConditionList">DependencyCondition!$A$2:$A$1000</definedName>
   </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,17 +39,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="9">
@@ -60,44 +52,44 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2F5597"/>
-        <bgColor rgb="FF2F5597"/>
+        <fgColor rgb="002F5597"/>
+        <bgColor rgb="002F5597"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF548235"/>
-        <bgColor rgb="FF548235"/>
+        <fgColor rgb="00548235"/>
+        <bgColor rgb="00548235"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF31859B"/>
-        <bgColor rgb="FF31859B"/>
+        <fgColor rgb="0031859B"/>
+        <bgColor rgb="0031859B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC55A11"/>
-        <bgColor rgb="FFC55A11"/>
+        <fgColor rgb="00C55A11"/>
+        <bgColor rgb="00C55A11"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF808080"/>
-        <bgColor rgb="FF808080"/>
+        <fgColor rgb="00808080"/>
+        <bgColor rgb="00808080"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
-        <bgColor rgb="FF7030A0"/>
+        <fgColor rgb="007030A0"/>
+        <bgColor rgb="007030A0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBF8F00"/>
-        <bgColor rgb="FFBF8F00"/>
+        <fgColor rgb="00BF8F00"/>
+        <bgColor rgb="00BF8F00"/>
       </patternFill>
     </fill>
   </fills>
@@ -113,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -136,12 +128,9 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -257,48 +246,55 @@
       <text>
         <t>Type: BIT
 Nullable: No
+Default: 1</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Type: BIT
+Nullable: No
 Default: 0</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>Type: INT
 Nullable: No
 Default: 4</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Type: TIME(0)
 Nullable: Yes</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Type: NVARCHAR(MAX)
 Nullable: Yes</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>Type: NVARCHAR(MAX)
 Nullable: Yes</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>Type: VARCHAR(200)
 Nullable: Yes
 FK -&gt; orch.ObjectIDs (WorkspaceName,JobName)=(WorkspaceName,ObjectName)</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>Type: NVARCHAR(100)
 Nullable: Yes</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>Type: TINYINT
 Nullable: No
@@ -552,22 +548,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblJobs" displayName="tblJobs" ref="A1:M2" headerRowCount="1">
-  <autoFilter ref="A1:M2"/>
-  <tableColumns count="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblJobs" displayName="tblJobs" ref="A1:N2" headerRowCount="1">
+  <autoFilter ref="A1:N2"/>
+  <tableColumns count="14">
     <tableColumn id="1" name="JobName"/>
     <tableColumn id="2" name="Include"/>
     <tableColumn id="3" name="TimeoutInSeconds"/>
     <tableColumn id="4" name="Retries"/>
     <tableColumn id="5" name="RetryIntervalInSeconds"/>
-    <tableColumn id="6" name="UpdateParallelBatchLimit"/>
-    <tableColumn id="7" name="ParallelBatchLimit"/>
-    <tableColumn id="8" name="ScheduledStartUTC"/>
-    <tableColumn id="9" name="ParametersJson"/>
-    <tableColumn id="10" name="Dependencies"/>
-    <tableColumn id="11" name="WorkspaceName"/>
-    <tableColumn id="12" name="Environment"/>
-    <tableColumn id="13" name="LoggingLevel"/>
+    <tableColumn id="6" name="UpdateObjectIDs"/>
+    <tableColumn id="7" name="UpdateParallelBatchLimit"/>
+    <tableColumn id="8" name="ParallelBatchLimit"/>
+    <tableColumn id="9" name="ScheduledStartUTC"/>
+    <tableColumn id="10" name="ParametersJson"/>
+    <tableColumn id="11" name="Dependencies"/>
+    <tableColumn id="12" name="WorkspaceName"/>
+    <tableColumn id="13" name="Environment"/>
+    <tableColumn id="14" name="LoggingLevel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -575,7 +572,7 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblTasks" displayName="tblTasks" ref="A1:N28" headerRowCount="1">
-  <autoFilter ref="A1:N28"/>
+  <autoFilter ref="A1:N2"/>
   <tableColumns count="14">
     <tableColumn id="1" name="TaskName"/>
     <tableColumn id="2" name="Include"/>
@@ -622,7 +619,7 @@
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="tblDependencyCondition" displayName="tblDependencyCondition" ref="A1:A4" headerRowCount="1">
-  <autoFilter ref="A1:A4"/>
+  <autoFilter ref="A1:A2"/>
   <tableColumns count="1">
     <tableColumn id="1" name="DependencyCondition"/>
   </tableColumns>
@@ -643,7 +640,7 @@
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="tblObjectIDs" displayName="tblObjectIDs" ref="A1:D4" headerRowCount="1">
-  <autoFilter ref="A1:D4"/>
+  <autoFilter ref="A1:D2"/>
   <tableColumns count="4">
     <tableColumn id="1" name="WorkspaceName"/>
     <tableColumn id="2" name="ObjectName"/>
@@ -940,26 +937,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF2F5597"/>
+    <tabColor rgb="002F5597"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24.36328125" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -988,42 +986,47 @@
           <t>RetryIntervalInSeconds</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>UpdateObjectIDs</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>UpdateParallelBatchLimit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ParallelBatchLimit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ScheduledStartUTC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ParametersJson</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>WorkspaceName</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LoggingLevel</t>
         </is>
@@ -1048,35 +1051,41 @@
         <v>60</v>
       </c>
       <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="b">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>4</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Wave MDF CentralHub</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>DEV</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>WorkspaceNameList</formula1>
-    </dataValidation>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>WorkspaceNameList</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1090,22 +1099,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF548235"/>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33.08984375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="13"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -1197,7 +1210,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1254,7 +1267,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1311,7 +1324,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1368,7 +1381,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1425,7 +1438,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1482,7 +1495,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1539,7 +1552,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1596,7 +1609,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1653,7 +1666,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1710,7 +1723,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1767,7 +1780,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1824,7 +1837,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1881,7 +1894,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1938,7 +1951,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1995,7 +2008,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2052,7 +2065,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2109,7 +2122,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2166,7 +2179,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2223,7 +2236,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2280,7 +2293,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2337,7 +2350,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2394,7 +2407,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2451,7 +2464,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2508,7 +2521,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2565,7 +2578,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2622,7 +2635,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2679,7 +2692,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2749,11 +2762,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0031859B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -2778,8 +2792,11 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="A2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>JobNameList</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>JobNameList</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2797,11 +2814,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C55A11"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
@@ -2826,8 +2844,11 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="A2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>TaskNameList</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>TaskNameList</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2845,11 +2866,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
   </cols>
@@ -2894,11 +2916,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
@@ -2943,14 +2966,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -2984,12 +3009,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nb_CopyTableToBronze</t>
+          <t>nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PENDING_DEPLOYMENT_REPLACE_ME_nb_CopyTableToBronze</t>
+          <t>PENDING_DEPLOYMENT_REPLACE_ME_nb_CopyTableToLakehouse</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/MetadataSync/orch_metadata.xlsx
+++ b/MetadataSync/orch_metadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paul\OneLake - Microsoft\Wave MDF CentralHub\lh_MetadataFileSync.Lakehouse\Files\MetadataSyncFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub_Repos\MDF_CentralHub\MetadataSync\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25397EB0-759C-4EBE-9A21-1F677A13DE12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A9C3B0-A18A-4FB9-80B8-C9B9CC39FF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21240" yWindow="-19890" windowWidth="25380" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22950" yWindow="-18180" windowWidth="25380" windowHeight="16245" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jobs" sheetId="1" r:id="rId1"/>
@@ -24,10 +24,10 @@
   <definedNames>
     <definedName name="DependencyConditionList">DependencyCondition!$A$2:$A$1000</definedName>
     <definedName name="JobNameList">Jobs!$A$2:$A$1000</definedName>
-    <definedName name="ObjectNameList">ObjectIDs!$B$2:$B$998</definedName>
+    <definedName name="ObjectNameList">ObjectIDs!$B$2:$B$999</definedName>
     <definedName name="TaskNameList">Tasks!$A$2:$A$1000</definedName>
     <definedName name="TaskTypeList">TaskType!$A$2:$A$1000</definedName>
-    <definedName name="WorkspaceNameList">ObjectIDs!$A$2:$A$998</definedName>
+    <definedName name="WorkspaceNameList">ObjectIDs!$A$2:$A$999</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -730,7 +730,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="99">
   <si>
     <t>JobName</t>
   </si>
@@ -1012,13 +1012,33 @@
   </si>
   <si>
     <t>Append</t>
+  </si>
+  <si>
+    <t>CopyBronze_WeatherGovDailyForecast</t>
+  </si>
+  <si>
+    <t>nb_WeatherGovApi_ToLakehouse</t>
+  </si>
+  <si>
+    <t>{"latitude": 39.7456, "longitude": -94.6238, ' +
+    '"userAgent": "MDF_CentralHub-demo (REPLACE_ME@yourdomain.example)", ' +
+    '"destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", ' +
+    '"destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0", ' +
+    '"destSchema": "dbo", "destTable": "WeatherGovDailyForecast", ' +
+    '"updateOption": "Append"}</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>PLACEHOLDER</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1038,6 +1058,11 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Cascadia Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1102,7 +1127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1130,6 +1155,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1172,8 +1203,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblTasks" displayName="tblTasks" ref="A1:O28">
-  <autoFilter ref="A1:O28" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblTasks" displayName="tblTasks" ref="A1:O29">
+  <autoFilter ref="A1:O29" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="TaskName"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Include"/>
@@ -1241,8 +1272,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="tblObjectIDs" displayName="tblObjectIDs" ref="A1:D2">
-  <autoFilter ref="A1:D2" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="tblObjectIDs" displayName="tblObjectIDs" ref="A1:D3">
+  <autoFilter ref="A1:D3" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="WorkspaceName"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="ObjectName"/>
@@ -1660,13 +1691,13 @@
   <sheetPr>
     <tabColor rgb="FF548235"/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="43.08984375" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="5" max="5" width="20.1796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="9" width="26" customWidth="1"/>
@@ -2908,6 +2939,50 @@
         <v>25</v>
       </c>
       <c r="O28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" t="b">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29">
+        <v>1800</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>30</v>
+      </c>
+      <c r="I29" t="s">
+        <v>93</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="L29" t="s">
+        <v>23</v>
+      </c>
+      <c r="M29" t="s">
+        <v>97</v>
+      </c>
+      <c r="N29" t="s">
+        <v>25</v>
+      </c>
+      <c r="O29">
         <v>1</v>
       </c>
     </row>
@@ -2925,7 +3000,7 @@
     <dataValidation type="list" allowBlank="1" sqref="E2:E1000" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>WorkspaceNameList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D1000" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D28 D30:D1000" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>ObjectNameList</formula1>
     </dataValidation>
   </dataValidations>
@@ -3091,12 +3166,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="20.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="61.7265625" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="55.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3125,6 +3200,20 @@
         <v>88</v>
       </c>
       <c r="D2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" t="s">
         <v>89</v>
       </c>
     </row>

--- a/MetadataSync/orch_metadata.xlsx
+++ b/MetadataSync/orch_metadata.xlsx
@@ -1248,7 +1248,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimAccount"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimAccount", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimChannel"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimChannel", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimCurrency"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimCurrency", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimCustomer"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimCustomer", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimDate"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimDate", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimEmployee"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimEmployee", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimEntity"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimEntity", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimGeography"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimGeography", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimMachine"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimMachine", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimOutage"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimOutage", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimProduct"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimProduct", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimProductCategory"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimProductCategory", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimProductSubcategory"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimProductSubcategory", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimPromotion"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimPromotion", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimSalesTerritory"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimSalesTerritory", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimScenario"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimScenario", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "DimStore"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "DimStore", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "FactExchangeRate"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "FactExchangeRate", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "FactInventory"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "FactInventory", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "FactITMachine"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "FactITMachine", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "FactITSLA"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "FactITSLA", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "FactOnlineSales"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "FactOnlineSales", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "FactSales"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "FactSales", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "FactSalesQuota"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "FactSalesQuota", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "FactSalesSmall"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "FactSalesSmall", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "FactStrategyPlan"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "FactStrategyPlan", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>{"sourceSchema": "dbo", "sourceTable": "YearList"}</t>
+          <t>{"sourceSchema": "dbo", "sourceTable": "YearList", "destWorkspaceId": "947d3136-33ac-458a-be73-ac7dc38afaa5", "destLakehouseId": "649b7795-2e22-4627-8b25-9749a6f492f0"}</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="20.1796875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3245,8 +3245,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/MetadataSync/orch_metadata.xlsx
+++ b/MetadataSync/orch_metadata.xlsx
@@ -5,28 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub_Repos\MDF_CentralHub\MetadataSync\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paul\AppData\Local\Temp\claude\C--Users-paul--claude--sessions\f349cfc3-19d3-4a4d-ad00-4498042b2edc\scratchpad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7647AEE-8AAC-4733-887D-AC44FAFED117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAE217D4-49BE-47F5-8549-B8B6CB5A1BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30675" yWindow="-17250" windowWidth="29415" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31995" yWindow="-16995" windowWidth="29415" windowHeight="16245" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jobs" sheetId="1" r:id="rId1"/>
     <sheet name="Tasks" sheetId="2" r:id="rId2"/>
-    <sheet name="JobDependencies" sheetId="3" r:id="rId3"/>
-    <sheet name="TaskDependencies" sheetId="4" r:id="rId4"/>
-    <sheet name="DependencyCondition" sheetId="5" r:id="rId5"/>
-    <sheet name="TaskType" sheetId="6" r:id="rId6"/>
-    <sheet name="ObjectIDs" sheetId="7" r:id="rId7"/>
-    <sheet name="Lookups" sheetId="8" r:id="rId8"/>
+    <sheet name="TaskParameters" sheetId="9" r:id="rId3"/>
+    <sheet name="JobDependencies" sheetId="3" r:id="rId4"/>
+    <sheet name="TaskDependencies" sheetId="4" r:id="rId5"/>
+    <sheet name="DependencyCondition" sheetId="5" r:id="rId6"/>
+    <sheet name="TaskType" sheetId="6" r:id="rId7"/>
+    <sheet name="ObjectIDs" sheetId="7" r:id="rId8"/>
+    <sheet name="Lookups" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="DependencyConditionList">DependencyCondition!$A$2:$A$1000</definedName>
     <definedName name="JobNameList">Jobs!$A$2:$A$1000</definedName>
     <definedName name="ObjectNameList">ObjectIDs!$B$2:$B$998</definedName>
-    <definedName name="TaskNameList">Tasks!$A$2:$A$983</definedName>
+    <definedName name="TaskNameList">Tasks!$A$2:$A$975</definedName>
     <definedName name="TaskTypeList">TaskType!$A$2:$A$1000</definedName>
     <definedName name="TaskUpdateOption">tblTaskUpdateOption[UpdateOption]</definedName>
     <definedName name="WorkspaceNameList">ObjectIDs!$A$2:$A$998</definedName>
@@ -732,7 +733,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="56">
   <si>
     <t>TaskName</t>
   </si>
@@ -785,51 +786,9 @@
     <t>Notebook</t>
   </si>
   <si>
-    <t>ContosoDW</t>
-  </si>
-  <si>
     <t>Bronze</t>
   </si>
   <si>
-    <t>CopyBronze_DimChannel</t>
-  </si>
-  <si>
-    <t>CopyBronze_DimCurrency</t>
-  </si>
-  <si>
-    <t>CopyBronze_DimCustomer</t>
-  </si>
-  <si>
-    <t>CopyBronze_DimDate</t>
-  </si>
-  <si>
-    <t>CopyBronze_DimEmployee</t>
-  </si>
-  <si>
-    <t>CopyBronze_DimGeography</t>
-  </si>
-  <si>
-    <t>CopyBronze_DimProduct</t>
-  </si>
-  <si>
-    <t>CopyBronze_DimProductCategory</t>
-  </si>
-  <si>
-    <t>CopyBronze_DimProductSubcategory</t>
-  </si>
-  <si>
-    <t>CopyBronze_FactOnlineSales</t>
-  </si>
-  <si>
-    <t>CopyBronze_WeatherGovDailyForecast</t>
-  </si>
-  <si>
-    <t>nb_WeatherGovApi_ToLakehouse</t>
-  </si>
-  <si>
-    <t>Weather</t>
-  </si>
-  <si>
     <t>UpdateObjectIDs</t>
   </si>
   <si>
@@ -878,39 +837,6 @@
     <t>WorkspaceID</t>
   </si>
   <si>
-    <t>TestJob1</t>
-  </si>
-  <si>
-    <t>{"sourceSchema": "dbo", "sourceTable": "DimChannel", "destWorkspaceId": "22273b40-4352-4cd5-aa68-cfc1d0f100cc", "destLakehouseId": "a3614891-8c2c-4a33-a78d-7dfedea10306"}</t>
-  </si>
-  <si>
-    <t>{"sourceSchema": "dbo", "sourceTable": "DimCurrency", "destWorkspaceId": "22273b40-4352-4cd5-aa68-cfc1d0f100cc", "destLakehouseId": "a3614891-8c2c-4a33-a78d-7dfedea10306"}</t>
-  </si>
-  <si>
-    <t>{"sourceSchema": "dbo", "sourceTable": "DimCustomer", "destWorkspaceId": "22273b40-4352-4cd5-aa68-cfc1d0f100cc", "destLakehouseId": "a3614891-8c2c-4a33-a78d-7dfedea10306"}</t>
-  </si>
-  <si>
-    <t>{"sourceSchema": "dbo", "sourceTable": "DimDate", "destWorkspaceId": "22273b40-4352-4cd5-aa68-cfc1d0f100cc", "destLakehouseId": "a3614891-8c2c-4a33-a78d-7dfedea10306"}</t>
-  </si>
-  <si>
-    <t>{"sourceSchema": "dbo", "sourceTable": "DimEmployee", "destWorkspaceId": "22273b40-4352-4cd5-aa68-cfc1d0f100cc", "destLakehouseId": "a3614891-8c2c-4a33-a78d-7dfedea10306"}</t>
-  </si>
-  <si>
-    <t>{"sourceSchema": "dbo", "sourceTable": "DimProduct", "destWorkspaceId": "22273b40-4352-4cd5-aa68-cfc1d0f100cc", "destLakehouseId": "a3614891-8c2c-4a33-a78d-7dfedea10306"}</t>
-  </si>
-  <si>
-    <t>{"sourceSchema": "dbo", "sourceTable": "DimGeography", "destWorkspaceId": "22273b40-4352-4cd5-aa68-cfc1d0f100cc", "destLakehouseId": "a3614891-8c2c-4a33-a78d-7dfedea10306"}</t>
-  </si>
-  <si>
-    <t>{"sourceSchema": "dbo", "sourceTable": "DimProductCategory", "destWorkspaceId": "22273b40-4352-4cd5-aa68-cfc1d0f100cc", "destLakehouseId": "a3614891-8c2c-4a33-a78d-7dfedea10306"}</t>
-  </si>
-  <si>
-    <t>{"sourceSchema": "dbo", "sourceTable": "DimProductSubcategory", "destWorkspaceId": "22273b40-4352-4cd5-aa68-cfc1d0f100cc", "destLakehouseId": "a3614891-8c2c-4a33-a78d-7dfedea10306"}</t>
-  </si>
-  <si>
-    <t>{"latitude": 39.7456, "longitude": -94.6238, "userAgent": "MDF_CentralHub-demo (REPLACE_ME@yourdomain.example)", "destWorkspaceId": "22273b40-4352-4cd5-aa68-cfc1d0f100cc", "destLakehouseId": "a3614891-8c2c-4a33-a78d-7dfedea10306", "destSchema": "dbo", "destTable": "WeatherGovDailyForecast", "updateOption": "Append"}</t>
-  </si>
-  <si>
     <t>Pipeline</t>
   </si>
   <si>
@@ -926,12 +852,6 @@
     <t>DMI Sensing CentralHub DEV</t>
   </si>
   <si>
-    <t>nb_CopySqlDemoTableToLakehouse</t>
-  </si>
-  <si>
-    <t>{"sourceSchema": "dbo", "sourceTable": "FactOnlineSales", "destWorkspaceId": "22273b40-4352-4cd5-aa68-cfc1d0f100cc", "destLakehouseId": "a3614891-8c2c-4a33-a78d-7dfedea10306"}</t>
-  </si>
-  <si>
     <t>Overwrite</t>
   </si>
   <si>
@@ -942,13 +862,52 @@
   </si>
   <si>
     <t>RefreshMetadata</t>
+  </si>
+  <si>
+    <t>Daily_Metrics</t>
+  </si>
+  <si>
+    <t>nb_Bronze_Metadata</t>
+  </si>
+  <si>
+    <t>SensingMetrics</t>
+  </si>
+  <si>
+    <t>nb_Bronze_Generic</t>
+  </si>
+  <si>
+    <t>CopyBronze_Dimensions</t>
+  </si>
+  <si>
+    <t>CopyBronze_Metadata</t>
+  </si>
+  <si>
+    <t>CopyBronze_Altmetric</t>
+  </si>
+  <si>
+    <t>CopyBronze_Talkwalker</t>
+  </si>
+  <si>
+    <t>{"source_name": "dimensions"}</t>
+  </si>
+  <si>
+    <t>{"source_name": "altmetric"}</t>
+  </si>
+  <si>
+    <t>{"source_name": "talkwalker_engagements"}</t>
+  </si>
+  <si>
+    <t>ParameterName</t>
+  </si>
+  <si>
+    <t>Value</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -968,11 +927,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Cascadia Mono"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1043,7 +997,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1072,12 +1026,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1120,8 +1068,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblTasks" displayName="tblTasks" ref="A1:O12">
-  <autoFilter ref="A1:O12" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="tblTasks" displayName="tblTasks" ref="A1:O5">
+  <autoFilter ref="A1:O5" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="TaskName"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Include"/>
@@ -1144,6 +1092,18 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{2B46A429-D918-45C3-98C4-09028307F81F}" name="tblTaskParameters" displayName="tblTaskParameters" ref="A1:C2" totalsRowShown="0">
+  <autoFilter ref="A1:C2" xr:uid="{2B46A429-D918-45C3-98C4-09028307F81F}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{E03B115A-1606-4C6C-9E34-AAB77B7709ED}" name="TaskName"/>
+    <tableColumn id="2" xr3:uid="{038CDA31-F67F-441E-94EA-99F3A33730DD}" name="ParameterName"/>
+    <tableColumn id="3" xr3:uid="{2261A51C-7C6F-4D9B-849C-18E9557B0FC0}" name="Value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="tblJobDependencies" displayName="tblJobDependencies" ref="A1:C2">
   <autoFilter ref="A1:C2" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
@@ -1155,7 +1115,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblTaskDependencies" displayName="tblTaskDependencies" ref="A1:C2">
   <autoFilter ref="A1:C2" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="3">
@@ -1167,7 +1127,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="tblDependencyCondition" displayName="tblDependencyCondition" ref="A1:A4">
   <autoFilter ref="A1:A4" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="1">
@@ -1177,7 +1137,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="tblTaskType" displayName="tblTaskType" ref="A1:B6">
   <autoFilter ref="A1:B6" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="2">
@@ -1188,7 +1148,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="tblObjectIDs" displayName="tblObjectIDs" ref="A1:D2" insertRow="1">
   <autoFilter ref="A1:D2" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="4">
@@ -1201,7 +1161,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{58E42C4D-5B9A-43DF-97F3-17F9D2250E11}" name="tblTaskUpdateOption" displayName="tblTaskUpdateOption" ref="A3:A5" totalsRowShown="0">
   <autoFilter ref="A3:A5" xr:uid="{58E42C4D-5B9A-43DF-97F3-17F9D2250E11}"/>
   <tableColumns count="1">
@@ -1534,19 +1494,19 @@
         <v>7</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>9</v>
@@ -1558,7 +1518,7 @@
         <v>4</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>14</v>
@@ -1566,7 +1526,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
@@ -1590,13 +1550,13 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M2" t="s">
         <v>15</v>
       </c>
       <c r="N2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -1624,7 +1584,7 @@
   <sheetPr>
     <tabColor rgb="FF548235"/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="33.08984375" bestFit="1" customWidth="1"/>
@@ -1690,19 +1650,19 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F2">
         <v>1800</v>
@@ -1714,19 +1674,16 @@
         <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
         <v>16</v>
       </c>
       <c r="M2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N2" t="s">
         <v>17</v>
-      </c>
-      <c r="N2" t="s">
-        <v>18</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -1734,19 +1691,19 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F3">
         <v>1800</v>
@@ -1758,19 +1715,19 @@
         <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="J3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L3" t="s">
         <v>16</v>
       </c>
       <c r="M3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3" t="s">
         <v>17</v>
-      </c>
-      <c r="N3" t="s">
-        <v>18</v>
       </c>
       <c r="O3">
         <v>1</v>
@@ -1778,19 +1735,19 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F4">
         <v>1800</v>
@@ -1802,19 +1759,19 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="J4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L4" t="s">
         <v>16</v>
       </c>
       <c r="M4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" t="s">
         <v>17</v>
-      </c>
-      <c r="N4" t="s">
-        <v>18</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -1822,19 +1779,19 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F5">
         <v>1800</v>
@@ -1846,352 +1803,44 @@
         <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="J5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L5" t="s">
         <v>16</v>
       </c>
       <c r="M5" t="s">
+        <v>45</v>
+      </c>
+      <c r="N5" t="s">
         <v>17</v>
       </c>
-      <c r="N5" t="s">
-        <v>18</v>
-      </c>
       <c r="O5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" t="b">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6">
-        <v>1800</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>30</v>
-      </c>
-      <c r="I6" t="s">
-        <v>68</v>
-      </c>
-      <c r="J6" t="s">
-        <v>53</v>
-      </c>
-      <c r="L6" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" t="s">
-        <v>17</v>
-      </c>
-      <c r="N6" t="s">
-        <v>18</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" t="b">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7">
-        <v>1800</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>30</v>
-      </c>
-      <c r="I7" t="s">
-        <v>68</v>
-      </c>
-      <c r="J7" t="s">
-        <v>55</v>
-      </c>
-      <c r="L7" t="s">
-        <v>16</v>
-      </c>
-      <c r="M7" t="s">
-        <v>17</v>
-      </c>
-      <c r="N7" t="s">
-        <v>18</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" t="b">
-        <v>1</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8">
-        <v>1800</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>30</v>
-      </c>
-      <c r="I8" t="s">
-        <v>68</v>
-      </c>
-      <c r="J8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8" t="s">
-        <v>16</v>
-      </c>
-      <c r="M8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N8" t="s">
-        <v>18</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" t="b">
-        <v>1</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>64</v>
-      </c>
-      <c r="E9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9">
-        <v>1800</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>30</v>
-      </c>
-      <c r="I9" t="s">
-        <v>68</v>
-      </c>
-      <c r="J9" t="s">
-        <v>56</v>
-      </c>
-      <c r="L9" t="s">
-        <v>16</v>
-      </c>
-      <c r="M9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N9" t="s">
-        <v>18</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" t="b">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10">
-        <v>1800</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>30</v>
-      </c>
-      <c r="I10" t="s">
-        <v>68</v>
-      </c>
-      <c r="J10" t="s">
-        <v>57</v>
-      </c>
-      <c r="L10" t="s">
-        <v>16</v>
-      </c>
-      <c r="M10" t="s">
-        <v>17</v>
-      </c>
-      <c r="N10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" t="b">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11">
-        <v>1800</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>30</v>
-      </c>
-      <c r="I11" t="s">
-        <v>68</v>
-      </c>
-      <c r="J11" t="s">
-        <v>65</v>
-      </c>
-      <c r="L11" t="s">
-        <v>16</v>
-      </c>
-      <c r="M11" t="s">
-        <v>17</v>
-      </c>
-      <c r="N11" t="s">
-        <v>18</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" t="b">
-        <v>1</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12">
-        <v>1800</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>30</v>
-      </c>
-      <c r="I12" t="s">
-        <v>68</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="L12" t="s">
-        <v>16</v>
-      </c>
-      <c r="M12" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" t="s">
-        <v>18</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" sqref="D13:D983 D2:D11" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I5" xr:uid="{30C864DC-D469-4601-87BD-2EE2EA35E979}">
+      <formula1>TaskUpdateOption</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D2:D975" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>ObjectNameList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B983" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B975" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C983" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C975" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>JobNameList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L2:L983" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="L2:L975" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>TaskTypeList</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E983" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E975" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>WorkspaceNameList</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I12" xr:uid="{30C864DC-D469-4601-87BD-2EE2EA35E979}">
-      <formula1>TaskUpdateOption</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2203,6 +1852,40 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9476A2AF-C9F5-468F-8CBD-2CB07F49F477}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1000" xr:uid="{7F01FFE3-D18B-4223-BAFD-4C5A892F7BFE}">
+      <formula1>TaskNameList</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2217,10 +1900,10 @@
         <v>2</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2240,7 +1923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2255,10 +1938,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2278,7 +1961,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2288,22 +1971,22 @@
   <sheetData>
     <row r="1" spans="1:1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2315,7 +1998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2329,7 +2012,7 @@
         <v>11</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -2342,7 +2025,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
@@ -2350,7 +2033,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
@@ -2358,7 +2041,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="B5" t="b">
         <v>0</v>
@@ -2366,7 +2049,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
@@ -2386,7 +2069,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2405,10 +2088,10 @@
         <v>3</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2425,7 +2108,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF7E3DF9-B8CE-453B-8F7B-F646236C44D8}">
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2435,7 +2118,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
@@ -2445,12 +2128,12 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
